--- a/data/trans_bre/P1426-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1426-Habitat-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,99%</t>
+          <t>-1,65%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 1,45</t>
+          <t>-1,82; 1,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,45</t>
+          <t>-1,16; 1,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,65</t>
+          <t>-2,14; 1,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-61,03; 112,81</t>
+          <t>-61,96; 104,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-51,84; 153,84</t>
+          <t>-54,99; 148,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-29,48; 31,05</t>
+          <t>-28,24; 32,88</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>-0,25</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>-5,28%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,42</t>
+          <t>-0,7; 1,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,61</t>
+          <t>0,09; 2,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 3,08</t>
+          <t>-2,0; 1,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,77; 172,82</t>
+          <t>-44,43; 171,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 418,3</t>
+          <t>-1,61; 407,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,66; 115,82</t>
+          <t>-33,72; 26,73</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-12,85%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 2,15</t>
+          <t>-0,39; 2,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,94</t>
+          <t>-0,65; 1,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,39</t>
+          <t>-1,36; 2,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-45,73; 430,36</t>
+          <t>-43,33; 485,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-40,28; 235,67</t>
+          <t>-40,28; 227,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-61,38; 49,24</t>
+          <t>-30,23; 78,94</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-0,33</t>
+          <t>0,17</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-7,42%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,36</t>
+          <t>-1,02; 1,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,32</t>
+          <t>-1,06; 1,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,13</t>
+          <t>-1,29; 1,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-46,04; 122,54</t>
+          <t>-44,36; 138,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,59; 103,72</t>
+          <t>-44,66; 119,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,55; 31,17</t>
+          <t>-25,26; 47,77</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,98</t>
+          <t>-0,4; 0,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 1,2</t>
+          <t>-0,03; 1,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,08</t>
+          <t>-0,84; 0,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 78,93</t>
+          <t>-21,86; 79,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 102,25</t>
+          <t>-0,86; 113,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,49; 28,85</t>
+          <t>-16,28; 18,02</t>
         </is>
       </c>
     </row>
